--- a/event_registration_forms/031_sponsor_appreciation_dinner_rsvp--event_registration_forms.xlsx
+++ b/event_registration_forms/031_sponsor_appreciation_dinner_rsvp--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>last name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact email</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Example - example@example.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +621,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>guest count</t>
+          <t>Guest Count</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +644,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>guest names</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Guest Names</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Comma separated list of guest names</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +671,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>guest dietary restrictions</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Guest Dietary Restrictions</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Any dietary restrictions for guests?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -692,7 +704,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,7 +721,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -735,10 +747,14 @@
           <t>RSVP Date</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -758,10 +774,14 @@
           <t>RSVP Time</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HH -MM AM/PM</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -784,24 +804,24 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dietary_restrictions</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dietary restrictions</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +834,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rsvp</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rsvp</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,159 +857,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>rsvp_status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>RSVP Status</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>This is for internal use only</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>rsvp_date</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rsvp date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>rsvp_time</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rsvp time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rsvp_message</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rsvp message</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>guest_names</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>guest names</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>guest_count</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>guest count</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>guest_dietary_restrictions</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>guest dietary restrictions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1009,9 +895,9 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +925,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1056,46 +942,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rsvp_choices</t>
+          <t>rsvp_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rsvp_choices</t>
+          <t>rsvp_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
